--- a/assessment_forms/042_value_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/042_value_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -969,8 +969,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -998,12 +998,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'house'}</t>
+          <t>house</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'House'}</t>
+          <t>House</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'apartment'}</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Apartment'}</t>
+          <t>Apartment</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'increase'}</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Increase'}</t>
+          <t>Increase</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'decrease'}</t>
+          <t>decrease</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Decrease'}</t>
+          <t>Decrease</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'rent_increase'}</t>
+          <t>rent_increase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Rent increase'}</t>
+          <t>Rent increase</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'rent_decrease'}</t>
+          <t>rent_decrease</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Rent decrease'}</t>
+          <t>Rent decrease</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'market_change'}</t>
+          <t>market_change</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Market change'}</t>
+          <t>Market change</t>
         </is>
       </c>
     </row>
